--- a/results/reliability_eval/Llama-3-8B_toy-qa-dataset_sample_15_tokens_0.1_temp_first_thought_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_toy-qa-dataset_sample_15_tokens_0.1_temp_first_thought_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.615</v>
+        <v>0.6017526777020448</v>
       </c>
       <c r="B2" t="n">
-        <v>0.816411134727635</v>
+        <v>0.8033585357049083</v>
       </c>
       <c r="C2" t="n">
-        <v>0.615</v>
+        <v>0.6017526777020448</v>
       </c>
       <c r="D2" t="n">
-        <v>0.816411134727635</v>
+        <v>0.8033585357049083</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4086666666666666</v>
+        <v>0.3932570593962999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7606850490207919</v>
+        <v>0.7270758248329885</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9944444444444445</v>
+        <v>0.975900681596884</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9967740196078432</v>
+        <v>0.9894169060029074</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7523809523809524</v>
       </c>
     </row>
   </sheetData>
